--- a/РАБОЧИЙ СТОЛ/машины ПОКОМ КИ.xlsx
+++ b/РАБОЧИЙ СТОЛ/машины ПОКОМ КИ.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\РАБОЧИЙ СТОЛ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FE36C92-20AB-4768-8880-082203AE74D0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{478A3DD4-08D1-472C-A684-2E25A27ECFC1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="30">
   <si>
     <t>Бердянск</t>
   </si>
@@ -51,15 +51,6 @@
     <t>ПОЛУЧАТЕЛЬ</t>
   </si>
   <si>
-    <t>ОБЩИИЙ ВЕС</t>
-  </si>
-  <si>
-    <t>1 машина</t>
-  </si>
-  <si>
-    <t>2 машина</t>
-  </si>
-  <si>
     <t>3 машина</t>
   </si>
   <si>
@@ -97,6 +88,39 @@
   </si>
   <si>
     <t>НПК ЛП</t>
+  </si>
+  <si>
+    <t>Горняк Горловка</t>
+  </si>
+  <si>
+    <t>Горняк Луганск</t>
+  </si>
+  <si>
+    <t>ВЕС НЕТТО</t>
+  </si>
+  <si>
+    <t>ВЕС БРУТТО</t>
+  </si>
+  <si>
+    <t>ПАЛЛЕТЫ</t>
+  </si>
+  <si>
+    <t>Павленко (Мелитополь)</t>
+  </si>
+  <si>
+    <t>Коныгин</t>
+  </si>
+  <si>
+    <t>Обрыньба</t>
+  </si>
+  <si>
+    <t>1 машина на 27,06</t>
+  </si>
+  <si>
+    <t>1 машина на 26,06</t>
+  </si>
+  <si>
+    <t>Логистон (ПРС)</t>
   </si>
 </sst>
 </file>
@@ -141,7 +165,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -531,11 +555,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -544,14 +597,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
@@ -559,30 +606,54 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -863,404 +934,595 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.85546875" customWidth="1"/>
-    <col min="6" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="9.85546875" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="14" width="9.85546875" customWidth="1"/>
-    <col min="15" max="15" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" customWidth="1"/>
+    <col min="4" max="4" width="6.5703125" customWidth="1"/>
+    <col min="5" max="6" width="7.28515625" customWidth="1"/>
+    <col min="7" max="7" width="6" customWidth="1"/>
+    <col min="8" max="9" width="7.28515625" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="12" width="7.28515625" customWidth="1"/>
+    <col min="13" max="13" width="6" customWidth="1"/>
+    <col min="14" max="15" width="7.28515625" customWidth="1"/>
+    <col min="16" max="16" width="6" customWidth="1"/>
+    <col min="17" max="17" width="8.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="26"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="26"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="L1" s="26"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="O1" s="26"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="29"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="29"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1" s="29"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="23" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="26"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="N2" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="O2" s="24"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:17" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="23"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="21"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="13">
-        <f>B3-C3-F3-I3-L3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B3" s="28"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="8">
+        <f>B3-E3-H3-K3-N3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="13">
-        <f t="shared" ref="O4:O13" si="0">B4-C4-F4-I4-L4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B4" s="33"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="8">
+        <f t="shared" ref="Q4:Q19" si="0">B4-E4-H4-K4-N4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="13">
+      <c r="B5" s="33"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="13">
+      <c r="B6" s="33"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="13">
+        <v>9</v>
+      </c>
+      <c r="B7" s="33"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="13">
+        <v>15</v>
+      </c>
+      <c r="B8" s="33"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="13">
+      <c r="B9" s="33"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="38"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="38"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="38"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="8"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="38"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="38"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="33"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="38"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="8">
+        <f t="shared" ref="Q16:Q18" si="1">B16-E16-H16-K16-N16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="13">
+      <c r="B17" s="38"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="38"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="38"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="13">
-        <f t="shared" ref="O12" si="1">B12-C12-F12-I12-L12</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="19">
-        <f>SUM(B3:B13)</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="18">
-        <f>SUM(C3:C13)</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="20">
-        <f t="shared" ref="D14:K14" si="2">SUM(D3:D13)</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="21">
+    <row r="20" spans="1:17" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="13">
+        <f t="shared" ref="B20:M20" si="2">SUM(B3:B19)</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F14" s="18">
+      <c r="D20" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G14" s="20">
+      <c r="E20" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H14" s="21">
+      <c r="F20" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I14" s="18">
+      <c r="G20" s="15">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J14" s="20">
+      <c r="H20" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K14" s="21">
+      <c r="I20" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L14" s="18">
-        <f t="shared" ref="L14:N14" si="3">SUM(L3:L13)</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="20">
+      <c r="J20" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M20" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N20" s="12">
+        <f t="shared" ref="N20:P20" si="3">SUM(N3:N19)</f>
+        <v>0</v>
+      </c>
+      <c r="O20" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N14" s="21">
+      <c r="P20" s="15">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O14" s="22">
-        <f>SUM(O3:O13)</f>
+      <c r="Q20" s="16">
+        <f>SUM(Q3:Q19)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <f>B20/17500</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="O1:O2"/>
+  <mergeCells count="9">
+    <mergeCell ref="Q1:Q2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/РАБОЧИЙ СТОЛ/машины ПОКОМ КИ.xlsx
+++ b/РАБОЧИЙ СТОЛ/машины ПОКОМ КИ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{478A3DD4-08D1-472C-A684-2E25A27ECFC1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEC27C70-F526-460E-AD45-8F88B6EA667D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -615,6 +615,21 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -639,21 +654,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -953,47 +953,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="26"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="22" t="s">
+      <c r="F1" s="41"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="26"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="22" t="s">
+      <c r="I1" s="41"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="26"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="22" t="s">
+      <c r="L1" s="41"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="O1" s="26"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="20" t="s">
+      <c r="O1" s="41"/>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="35" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="23"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
+      <c r="A2" s="38"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
       <c r="E2" s="17" t="s">
         <v>11</v>
       </c>
@@ -1030,18 +1030,18 @@
       <c r="P2" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="Q2" s="21"/>
+      <c r="Q2" s="36"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="32"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="24"/>
       <c r="H3" s="6"/>
       <c r="I3" s="3"/>
       <c r="J3" s="7"/>
@@ -1060,12 +1060,12 @@
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="37"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="29"/>
       <c r="H4" s="4"/>
       <c r="I4" s="2"/>
       <c r="J4" s="5"/>
@@ -1084,12 +1084,12 @@
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="33"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="37"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="29"/>
       <c r="H5" s="4"/>
       <c r="I5" s="2"/>
       <c r="J5" s="5"/>
@@ -1108,12 +1108,12 @@
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="37"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="29"/>
       <c r="H6" s="4"/>
       <c r="I6" s="2"/>
       <c r="J6" s="5"/>
@@ -1132,12 +1132,12 @@
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="33"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="37"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="29"/>
       <c r="H7" s="4"/>
       <c r="I7" s="2"/>
       <c r="J7" s="5"/>
@@ -1156,12 +1156,12 @@
       <c r="A8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="37"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="29"/>
       <c r="H8" s="4"/>
       <c r="I8" s="2"/>
       <c r="J8" s="5"/>
@@ -1180,12 +1180,12 @@
       <c r="A9" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="33"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="37"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="29"/>
       <c r="H9" s="4"/>
       <c r="I9" s="2"/>
       <c r="J9" s="5"/>
@@ -1204,12 +1204,12 @@
       <c r="A10" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="38"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="42"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="9"/>
       <c r="I10" s="10"/>
       <c r="J10" s="11"/>
@@ -1228,12 +1228,12 @@
       <c r="A11" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="38"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="42"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="34"/>
       <c r="H11" s="9"/>
       <c r="I11" s="10"/>
       <c r="J11" s="11"/>
@@ -1252,12 +1252,12 @@
       <c r="A12" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="38"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="42"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="34"/>
       <c r="H12" s="9"/>
       <c r="I12" s="10"/>
       <c r="J12" s="11"/>
@@ -1267,18 +1267,21 @@
       <c r="N12" s="9"/>
       <c r="O12" s="10"/>
       <c r="P12" s="11"/>
-      <c r="Q12" s="8"/>
+      <c r="Q12" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="38"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="42"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="34"/>
       <c r="H13" s="9"/>
       <c r="I13" s="10"/>
       <c r="J13" s="11"/>
@@ -1297,12 +1300,12 @@
       <c r="A14" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="38"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="42"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="34"/>
       <c r="H14" s="9"/>
       <c r="I14" s="10"/>
       <c r="J14" s="11"/>
@@ -1321,12 +1324,12 @@
       <c r="A15" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="33"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="37"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="29"/>
       <c r="H15" s="4"/>
       <c r="I15" s="2"/>
       <c r="J15" s="5"/>
@@ -1345,12 +1348,12 @@
       <c r="A16" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="38"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="42"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="34"/>
       <c r="H16" s="9"/>
       <c r="I16" s="10"/>
       <c r="J16" s="11"/>
@@ -1369,12 +1372,12 @@
       <c r="A17" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="38"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="42"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="34"/>
       <c r="H17" s="9"/>
       <c r="I17" s="10"/>
       <c r="J17" s="11"/>
@@ -1393,12 +1396,12 @@
       <c r="A18" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="38"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="42"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="34"/>
       <c r="H18" s="9"/>
       <c r="I18" s="10"/>
       <c r="J18" s="11"/>
@@ -1417,12 +1420,12 @@
       <c r="A19" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="38"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="42"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="34"/>
       <c r="H19" s="9"/>
       <c r="I19" s="10"/>
       <c r="J19" s="11"/>

--- a/РАБОЧИЙ СТОЛ/машины ПОКОМ КИ.xlsx
+++ b/РАБОЧИЙ СТОЛ/машины ПОКОМ КИ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEC27C70-F526-460E-AD45-8F88B6EA667D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51EDBD34-4640-4183-B238-566020FDBBD0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -165,7 +165,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -374,10 +374,36 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -385,14 +411,98 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -405,190 +515,16 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -597,15 +533,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -615,25 +551,19 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -953,47 +883,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="D1" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="41"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="37" t="s">
+      <c r="F1" s="35"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="41"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="37" t="s">
+      <c r="I1" s="35"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="41"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="37" t="s">
+      <c r="L1" s="35"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="35" t="s">
+      <c r="O1" s="35"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="29" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="38"/>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
       <c r="E2" s="17" t="s">
         <v>11</v>
       </c>
@@ -1030,7 +960,7 @@
       <c r="P2" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="Q2" s="36"/>
+      <c r="Q2" s="30"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -1038,10 +968,10 @@
       </c>
       <c r="B3" s="20"/>
       <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="24"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="22"/>
       <c r="H3" s="6"/>
       <c r="I3" s="3"/>
       <c r="J3" s="7"/>
@@ -1060,12 +990,12 @@
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="29"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="25"/>
       <c r="H4" s="4"/>
       <c r="I4" s="2"/>
       <c r="J4" s="5"/>
@@ -1084,12 +1014,12 @@
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="29"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="25"/>
       <c r="H5" s="4"/>
       <c r="I5" s="2"/>
       <c r="J5" s="5"/>
@@ -1108,12 +1038,12 @@
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="29"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="25"/>
       <c r="H6" s="4"/>
       <c r="I6" s="2"/>
       <c r="J6" s="5"/>
@@ -1132,12 +1062,12 @@
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="25"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="29"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="25"/>
       <c r="H7" s="4"/>
       <c r="I7" s="2"/>
       <c r="J7" s="5"/>
@@ -1156,12 +1086,12 @@
       <c r="A8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="29"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="25"/>
       <c r="H8" s="4"/>
       <c r="I8" s="2"/>
       <c r="J8" s="5"/>
@@ -1180,12 +1110,12 @@
       <c r="A9" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="25"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="29"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="25"/>
       <c r="H9" s="4"/>
       <c r="I9" s="2"/>
       <c r="J9" s="5"/>
@@ -1204,12 +1134,12 @@
       <c r="A10" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="30"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="34"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="28"/>
       <c r="H10" s="9"/>
       <c r="I10" s="10"/>
       <c r="J10" s="11"/>
@@ -1228,12 +1158,12 @@
       <c r="A11" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="30"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="34"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="28"/>
       <c r="H11" s="9"/>
       <c r="I11" s="10"/>
       <c r="J11" s="11"/>
@@ -1252,12 +1182,12 @@
       <c r="A12" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="34"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="28"/>
       <c r="H12" s="9"/>
       <c r="I12" s="10"/>
       <c r="J12" s="11"/>
@@ -1276,12 +1206,12 @@
       <c r="A13" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="30"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="34"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="28"/>
       <c r="H13" s="9"/>
       <c r="I13" s="10"/>
       <c r="J13" s="11"/>
@@ -1300,12 +1230,12 @@
       <c r="A14" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="30"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="34"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="28"/>
       <c r="H14" s="9"/>
       <c r="I14" s="10"/>
       <c r="J14" s="11"/>
@@ -1324,12 +1254,12 @@
       <c r="A15" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="25"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="29"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="25"/>
       <c r="H15" s="4"/>
       <c r="I15" s="2"/>
       <c r="J15" s="5"/>
@@ -1348,12 +1278,12 @@
       <c r="A16" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="30"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="34"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="28"/>
       <c r="H16" s="9"/>
       <c r="I16" s="10"/>
       <c r="J16" s="11"/>
@@ -1372,12 +1302,12 @@
       <c r="A17" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="30"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="34"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="28"/>
       <c r="H17" s="9"/>
       <c r="I17" s="10"/>
       <c r="J17" s="11"/>
@@ -1396,12 +1326,12 @@
       <c r="A18" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="30"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="34"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="28"/>
       <c r="H18" s="9"/>
       <c r="I18" s="10"/>
       <c r="J18" s="11"/>
@@ -1420,12 +1350,12 @@
       <c r="A19" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="30"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="34"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="28"/>
       <c r="H19" s="9"/>
       <c r="I19" s="10"/>
       <c r="J19" s="11"/>
